--- a/results/01_pollution_assessment/SumRel_Focus/tables/varpart_summary.xlsx
+++ b/results/01_pollution_assessment/SumRel_Focus/tables/varpart_summary.xlsx
@@ -470,25 +470,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.2178321829613599</v>
+        <v>0.1702451500749244</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09549551191177152</v>
+        <v>0.08018347742379506</v>
       </c>
       <c r="D2" t="n">
-        <v>0.266981474782112</v>
+        <v>0.1596926191844441</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1714859628703405</v>
+        <v>0.07950914176064905</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04634622009101941</v>
+        <v>0.09073600831427531</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04914929182075212</v>
+        <v>-0.01055253089048025</v>
       </c>
       <c r="H2" t="n">
-        <v>0.733018525217888</v>
+        <v>0.8403073808155559</v>
       </c>
     </row>
   </sheetData>

--- a/results/01_pollution_assessment/SumRel_Focus/tables/varpart_summary.xlsx
+++ b/results/01_pollution_assessment/SumRel_Focus/tables/varpart_summary.xlsx
@@ -470,25 +470,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.1702451500749244</v>
+        <v>0.1731727087315488</v>
       </c>
       <c r="C2" t="n">
-        <v>0.08018347742379506</v>
+        <v>0.07338547378105142</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1596926191844441</v>
+        <v>0.1800273410428279</v>
       </c>
       <c r="E2" t="n">
-        <v>0.07950914176064905</v>
+        <v>0.1066418672617765</v>
       </c>
       <c r="F2" t="n">
-        <v>0.09073600831427531</v>
+        <v>0.06653084146977228</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.01055253089048025</v>
+        <v>0.006854632311279141</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8403073808155559</v>
+        <v>0.8199726589571721</v>
       </c>
     </row>
   </sheetData>

--- a/results/01_pollution_assessment/SumRel_Focus/tables/varpart_summary.xlsx
+++ b/results/01_pollution_assessment/SumRel_Focus/tables/varpart_summary.xlsx
@@ -470,25 +470,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.1731727087315488</v>
+        <v>0.1249103550693458</v>
       </c>
       <c r="C2" t="n">
-        <v>0.07338547378105142</v>
+        <v>0.08854073659801875</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1800273410428279</v>
+        <v>0.2223100144740118</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1066418672617765</v>
+        <v>0.133769277875993</v>
       </c>
       <c r="F2" t="n">
-        <v>0.06653084146977228</v>
+        <v>-0.00885892280664724</v>
       </c>
       <c r="G2" t="n">
-        <v>0.006854632311279141</v>
+        <v>0.09739965940466599</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8199726589571721</v>
+        <v>0.7776899855259882</v>
       </c>
     </row>
   </sheetData>

--- a/results/01_pollution_assessment/SumRel_Focus/tables/varpart_summary.xlsx
+++ b/results/01_pollution_assessment/SumRel_Focus/tables/varpart_summary.xlsx
@@ -470,25 +470,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.1249103550693458</v>
+        <v>0.119982122181327</v>
       </c>
       <c r="C2" t="n">
-        <v>0.08854073659801875</v>
+        <v>0.07321168276111656</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2223100144740118</v>
+        <v>0.1843450698545298</v>
       </c>
       <c r="E2" t="n">
-        <v>0.133769277875993</v>
+        <v>0.1111333870934132</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.00885892280664724</v>
+        <v>0.008848735087913728</v>
       </c>
       <c r="G2" t="n">
-        <v>0.09739965940466599</v>
+        <v>0.06436294767320283</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7776899855259882</v>
+        <v>0.8156549301454702</v>
       </c>
     </row>
   </sheetData>
